--- a/Intro materials/Lab Schedule Spring 2026.xlsx
+++ b/Intro materials/Lab Schedule Spring 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsoliman/Library/CloudStorage/Dropbox/Clemson/Econometrics Course/Specific to Semesters/Spring 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895C0FD4-C4F5-424A-A85E-E9C9126CE552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14718EDA-D955-9849-9ADD-246601999F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4240" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{1103A02E-6F1A-EC41-B75E-F74E9889530B}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15180" xr2:uid="{1103A02E-6F1A-EC41-B75E-F74E9889530B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
   <si>
     <t>Help with final project</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Good coding practices and mapping data to graphics</t>
+  </si>
+  <si>
+    <t>Regression Inference</t>
   </si>
 </sst>
 </file>
@@ -636,7 +639,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -648,7 +651,7 @@
         <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -660,7 +663,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -672,7 +675,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -726,7 +729,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -738,7 +741,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
